--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>32.26</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.44</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分78.0分（基本面100/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>330.51</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>17.99</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>4.1</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>28.45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>19.23</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.22</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>86.26</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>14.83</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.11</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>41.35</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>6.87</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.91</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>55.39</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>24.08</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4.6</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>54.83</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.98</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.26</t>
+          <t>32.25</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=36.1中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=40.3中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -571,43 +571,43 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>330.51</t>
+          <t>28.63</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>17.99</v>
+        <v>19.35</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分74.0分（基本面78.0/技术面70.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=10.4超卖区；近20日已跌-16.1%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD金叉；MACD红柱放大；RSI=58.3中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,50 +622,50 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
+          <t>基本面78.0 / 技术面70.0 / 综合74.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>337.11</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19.23</v>
+        <v>18.35</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.22</v>
+        <v>4.18</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=56.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.8超卖区；近20日已跌-15.7%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面60.0 / 综合69.0</t>
+          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86.26</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.83</v>
+        <v>6.95</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.11</v>
+        <v>0.92</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=51.8中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.2中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,50 +738,50 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
+          <t>基本面72.0 / 技术面66.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41.35</t>
+          <t>54.73</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.87</v>
+        <v>6.22</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.91</v>
+        <v>0.98</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=68.2中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=53.8中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
+          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55.39</t>
+          <t>86.80</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>24.08</v>
+        <v>14.92</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.6</v>
+        <v>3.13</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=55.8中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=50.7中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
+          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>54.83</t>
+          <t>1277.96</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.23</v>
+        <v>19.62</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.98</v>
+        <v>6.36</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；MACD死叉；RSI=54.9中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=38.3中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,29 +912,29 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
+          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>宽基指数</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>1.61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分51.0分（基本面60.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分52.5分（基本面60.0/技术面45.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=41.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=39.6中性区；近20日已跌-14.6%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面42.0 / 综合51.0</t>
+          <t>基本面60.0 / 技术面45.0 / 综合52.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,18 +528,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.25</t>
+          <t>32.04</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.68</v>
+        <v>12.45</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.44</v>
+        <v>4.36</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分78.0分（基本面100/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分80.5分（基本面100/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=40.3中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=32.1超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面56.0 / 综合78.0</t>
+          <t>基本面100 / 技术面61.0 / 综合80.5</t>
         </is>
       </c>
     </row>
@@ -586,18 +586,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.63</t>
+          <t>28.50</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.35</v>
+        <v>19.26</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分74.0分（基本面78.0/技术面70.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD金叉；MACD红柱放大；RSI=58.3中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,50 +622,50 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面70.0 / 综合74.0</t>
+          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>337.11</t>
+          <t>54.13</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>18.35</v>
+        <v>6.13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4.18</v>
+        <v>0.97</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.8超卖区；近20日已跌-15.7%，接近超跌</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=44.1中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
+          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>316.36</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.95</v>
+        <v>17.22</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.92</v>
+        <v>3.93</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.7超卖区；近20日已跌-20.2%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,50 +738,50 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面66.0 / 综合69.0</t>
+          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>54.73</t>
+          <t>87.56</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.22</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.98</v>
+        <v>3.14</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=53.8中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=57.4中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,50 +796,50 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
+          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>86.80</t>
+          <t>41.10</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.92</v>
+        <v>6.83</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3.13</v>
+        <v>0.91</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=50.7中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=61.4中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1277.96</t>
+          <t>51.63</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.62</v>
+        <v>22.45</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6.36</v>
+        <v>4.29</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.5分（基本面84.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=38.3中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=31.4超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
+          <t>基本面84.0 / 技术面47.0 / 综合65.5</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分52.5分（基本面60.0/技术面45.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分54.5分（基本面60.0/技术面49.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=39.6中性区；近20日已跌-14.6%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.2中性区；近20日已跌-13.2%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面45.0 / 综合52.5</t>
+          <t>基本面60.0 / 技术面49.0 / 综合54.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.04</t>
+          <t>31.68</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=32.1超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=30.4超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54.13</t>
+          <t>53.90</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
@@ -665,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=44.1中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=43.0中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87.56</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
@@ -781,7 +781,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=57.4中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=55.5中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,18 +528,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>31.68</t>
+          <t>32.17</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.45</v>
+        <v>12.64</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.36</v>
+        <v>4.42</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分80.5分（基本面100/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分82.5分（基本面100/技术面65.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=30.4超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=34.0超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面61.0 / 综合80.5</t>
+          <t>基本面100 / 技术面65.0 / 综合82.5</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.50</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.26</v>
+        <v>19.24</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=54.9中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=57.1中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -629,43 +629,43 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53.90</t>
+          <t>305.48</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.13</v>
+        <v>16.63</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.97</v>
+        <v>3.79</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.0分（基本面87.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=43.0中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.0超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-21.5%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
+          <t>基本面87.0 / 技术面55.0 / 综合71.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>316.36</t>
+          <t>53.51</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>17.22</v>
+        <v>6.08</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.93</v>
+        <v>0.96</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.7超卖区；近20日已跌-20.2%，接近超跌</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=42.4中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
+          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
         </is>
       </c>
     </row>
@@ -760,18 +760,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87.23</t>
+          <t>85.00</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>15</v>
+        <v>14.61</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.14</v>
+        <v>3.06</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=55.5中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=43.9中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
+          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.10</t>
+          <t>52.89</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.83</v>
+        <v>22.99</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.91</v>
+        <v>4.4</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=61.4中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.5中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
+          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.63</t>
+          <t>40.92</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>22.45</v>
+        <v>6.8</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4.29</v>
+        <v>0.9</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面84.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分62.0分（基本面72.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=31.4超卖区</t>
+          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=61.9中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面47.0 / 综合65.5</t>
+          <t>基本面72.0 / 技术面52.0 / 综合62.0</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分54.5分（基本面60.0/技术面49.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分58.0分（基本面60.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.2中性区；近20日已跌-13.2%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.6中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面49.0 / 综合54.5</t>
+          <t>基本面60.0 / 技术面56.0 / 综合58.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,18 +528,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>31.68</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.64</v>
+        <v>12.45</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分82.5分（基本面100/技术面65.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分80.5分（基本面100/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=34.0超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=30.4超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面65.0 / 综合82.5</t>
+          <t>基本面100 / 技术面61.0 / 综合80.5</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>28.50</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.24</v>
+        <v>19.26</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=57.1中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -629,43 +629,43 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>305.48</t>
+          <t>53.90</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>16.63</v>
+        <v>6.13</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.79</v>
+        <v>0.97</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面87.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.0超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-21.5%，接近超跌</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=43.0中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面55.0 / 综合71.0</t>
+          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.51</t>
+          <t>316.36</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.08</v>
+        <v>17.22</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.96</v>
+        <v>3.93</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=42.4中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.7超卖区；近20日已跌-20.2%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
+          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
         </is>
       </c>
     </row>
@@ -760,18 +760,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>87.23</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.61</v>
+        <v>15</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.06</v>
+        <v>3.14</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=43.9中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=55.5中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
+          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52.89</t>
+          <t>41.10</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>22.99</v>
+        <v>6.83</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.4</v>
+        <v>0.91</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.5中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=61.4中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>51.63</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.8</v>
+        <v>22.45</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9</v>
+        <v>4.29</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分62.0分（基本面72.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.5分（基本面84.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=61.9中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=31.4超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面52.0 / 综合62.0</t>
+          <t>基本面84.0 / 技术面47.0 / 综合65.5</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分58.0分（基本面60.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分54.5分（基本面60.0/技术面49.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.6中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.2中性区；近20日已跌-13.2%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面56.0 / 综合58.0</t>
+          <t>基本面60.0 / 技术面49.0 / 综合54.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,18 +528,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>32.17</t>
+          <t>30.90</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.64</v>
+        <v>12.14</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.42</v>
+        <v>4.25</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分82.5分（基本面100/技术面65.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.5分（基本面100/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=34.0超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.5超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,50 +564,50 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面65.0 / 综合82.5</t>
+          <t>基本面100 / 技术面47.0 / 综合73.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>304.30</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.24</v>
+        <v>16.57</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.22</v>
+        <v>3.78</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.0分（基本面87.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=57.1中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；5日均量为60日均量的1.35倍，量能放大；近20日已跌-21.0%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,50 +622,50 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
+          <t>基本面87.0 / 技术面55.0 / 综合71.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>305.48</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>16.63</v>
+        <v>19.24</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.79</v>
+        <v>3.22</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面87.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.0超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-21.5%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面55.0 / 综合71.0</t>
+          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
         </is>
       </c>
     </row>
@@ -702,11 +702,11 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.51</t>
+          <t>53.35</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.08</v>
+        <v>6.06</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.96</v>
@@ -723,7 +723,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=42.4中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=41.7中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -760,11 +760,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.00</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.61</v>
+        <v>14.62</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>3.06</v>
@@ -781,7 +781,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=43.9中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=43.8中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -803,48 +803,48 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>52.89</t>
+          <t>40.60</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>22.99</v>
+        <v>6.75</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.4</v>
+        <v>0.89</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.5中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=60.9中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
+          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.92</t>
+          <t>52.13</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.8</v>
+        <v>22.67</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9</v>
+        <v>4.33</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分62.0分（基本面72.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分63.0分（基本面84.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=61.9中性区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=36.1中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,29 +912,29 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面52.0 / 综合62.0</t>
+          <t>基本面84.0 / 技术面42.0 / 综合63.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>588000</t>
+          <t>510300</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>科创50ETF</t>
+          <t>沪深300ETF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>宽基指数</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>4.53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分58.0分（基本面60.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分53.5分（基本面60.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.6中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=23.5超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面56.0 / 综合58.0</t>
+          <t>基本面60.0 / 技术面47.0 / 综合53.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -571,43 +571,43 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>304.30</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>16.57</v>
+        <v>19.24</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.78</v>
+        <v>3.22</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面87.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；5日均量为60日均量的1.35倍，量能放大；近20日已跌-21.0%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,50 +622,50 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面55.0 / 综合71.0</t>
+          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>53.35</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19.24</v>
+        <v>6.06</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.22</v>
+        <v>0.96</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=41.7中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
+          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>304.30</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.06</v>
+        <v>16.57</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.96</v>
+        <v>3.78</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=41.7中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；近20日已跌-21.0%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
+          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -571,43 +571,43 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>304.30</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.24</v>
+        <v>16.57</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.22</v>
+        <v>3.78</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.0分（基本面87.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；5日均量为60日均量的1.35倍，量能放大；近20日已跌-21.0%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,50 +622,50 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
+          <t>基本面87.0 / 技术面55.0 / 综合71.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>28.46</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.06</v>
+        <v>19.24</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.96</v>
+        <v>3.22</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=41.7中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
+          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>304.30</t>
+          <t>53.35</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>16.57</v>
+        <v>6.06</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.78</v>
+        <v>0.96</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；近20日已跌-21.0%，接近超跌</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=41.7中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
+          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,18 +528,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>30.90</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.14</v>
+        <v>12.35</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.25</v>
+        <v>4.32</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.5分（基本面100/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分80.0分（基本面100/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.5超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=36.3中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面47.0 / 综合73.5</t>
+          <t>基本面100 / 技术面60.0 / 综合80.0</t>
         </is>
       </c>
     </row>
@@ -586,18 +586,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>304.30</t>
+          <t>301.95</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>16.57</v>
+        <v>16.44</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面87.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.0分（基本面87.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=13.5超卖区；5日均量为60日均量的1.35倍，量能放大；近20日已跌-21.0%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.42倍，量能放大；近20日已跌-22.8%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,50 +622,50 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面55.0 / 综合71.0</t>
+          <t>基本面87.0 / 技术面59.0 / 综合73.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>53.37</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19.24</v>
+        <v>6.07</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.22</v>
+        <v>0.96</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=58.2中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=42.0中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
+          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>84.40</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.06</v>
+        <v>14.51</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.96</v>
+        <v>3.04</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分68.0分（基本面75.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=41.7中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=31.0超卖区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,50 +738,50 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
+          <t>基本面75.0 / 技术面61.0 / 综合68.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>28.27</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.62</v>
+        <v>19.11</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.06</v>
+        <v>3.2</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=43.8中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=53.4中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
+          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40.60</t>
+          <t>54.10</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.75</v>
+        <v>23.53</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.89</v>
+        <v>4.5</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=60.9中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.7中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
+          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52.13</t>
+          <t>40.59</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>22.67</v>
+        <v>6.75</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4.33</v>
+        <v>0.89</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分63.0分（基本面84.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=36.1中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=54.7中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面42.0 / 综合63.0</t>
+          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.53</t>
+          <t>4.58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分53.5分（基本面60.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分55.5分（基本面60.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=23.5超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.0超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面47.0 / 综合53.5</t>
+          <t>基本面60.0 / 技术面51.0 / 综合55.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.42倍，量能放大；近20日已跌-22.8%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.34倍，量能放大；近20日已跌-22.8%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.34倍，量能放大；近20日已跌-22.8%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.42倍，量能放大；近20日已跌-22.8%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>297.10</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.35</v>
+        <v>16.17</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.32</v>
+        <v>3.69</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分80.0分（基本面100/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.0分（基本面87.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=36.3中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=14.0超卖区；5日均量为60日均量的1.56倍，量能放大；近20日已跌-23.4%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,50 +564,50 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面60.0 / 综合80.0</t>
+          <t>基本面87.0 / 技术面59.0 / 综合73.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>有色金属</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>301.95</t>
+          <t>31.30</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>16.44</v>
+        <v>12.3</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.0分（基本面87.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=13.9超卖区；5日均量为60日均量的1.42倍，量能放大；近20日已跌-22.8%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.3中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面59.0 / 综合73.0</t>
+          <t>基本面100 / 技术面46.0 / 综合73.0</t>
         </is>
       </c>
     </row>
@@ -644,18 +644,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53.37</t>
+          <t>53.98</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.07</v>
+        <v>6.14</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=42.0中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=36.4中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
+          <t>基本面82.0 / 技术面60.0 / 综合71.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>84.40</t>
+          <t>41.04</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.51</v>
+        <v>6.82</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.04</v>
+        <v>0.9</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分68.0分（基本面75.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=31.0超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=51.9中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面61.0 / 综合68.0</t>
+          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
         </is>
       </c>
     </row>
@@ -760,18 +760,18 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28.27</t>
+          <t>28.10</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.11</v>
+        <v>18.99</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.0分（基本面78.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=53.4中性区</t>
+          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=44.0中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
+          <t>基本面78.0 / 技术面52.0 / 综合65.0</t>
         </is>
       </c>
     </row>
@@ -818,14 +818,14 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54.10</t>
+          <t>54.44</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>23.53</v>
+        <v>23.68</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.7中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=42.6中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -861,43 +861,43 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>40.59</t>
+          <t>80.90</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.75</v>
+        <v>13.91</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.89</v>
+        <v>2.91</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分61.0分（基本面75.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=54.7中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=22.6超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
+          <t>基本面75.0 / 技术面47.0 / 综合61.0</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.58</t>
+          <t>4.61</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分55.5分（基本面60.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分58.0分（基本面60.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.0超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.0中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面51.0 / 综合55.5</t>
+          <t>基本面60.0 / 技术面56.0 / 综合58.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>297.10</t>
+          <t>304.63</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>16.17</v>
+        <v>16.58</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.69</v>
+        <v>3.78</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=14.0超卖区；5日均量为60日均量的1.56倍，量能放大；近20日已跌-23.4%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.5超卖区；5日均量为60日均量的1.54倍，量能放大；近20日已跌-19.1%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -586,14 +586,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>31.30</t>
+          <t>31.41</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12.3</v>
+        <v>12.35</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.3中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.9中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -644,14 +644,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>53.98</t>
+          <t>54.46</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.14</v>
+        <v>6.19</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=36.4中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=42.8中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -687,48 +687,48 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>54.84</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.82</v>
+        <v>23.85</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9</v>
+        <v>4.56</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.0分（基本面84.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=51.9中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=43.4中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -738,50 +738,50 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面84.0 / 技术面56.0 / 综合70.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>28.10</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>18.99</v>
+        <v>6.79</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.18</v>
+        <v>0.9</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面78.0/技术面52.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；MACD死叉；RSI=44.0中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=49.5中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面52.0 / 综合65.0</t>
+          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>54.44</t>
+          <t>28.02</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>23.68</v>
+        <v>18.94</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.53</v>
+        <v>3.17</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分62.5分（基本面78.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=42.6中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=34.5超卖区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
+          <t>基本面78.0 / 技术面47.0 / 综合62.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>80.90</t>
+          <t>1253.80</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>13.91</v>
+        <v>19.25</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>2.91</v>
+        <v>6.24</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分61.0分（基本面75.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分62.0分（基本面73.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=22.6超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=33.8超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面47.0 / 综合61.0</t>
+          <t>基本面73.0 / 技术面51.0 / 综合62.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分58.0分（基本面60.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分53.0分（基本面60.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=39.0中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.8中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面56.0 / 综合58.0</t>
+          <t>基本面60.0 / 技术面46.0 / 综合53.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>304.63</t>
+          <t>53.87</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>16.58</v>
+        <v>6.12</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.78</v>
+        <v>0.97</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.0分（基本面87.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.5分（基本面82.0/技术面65.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.5超卖区；5日均量为60日均量的1.54倍，量能放大；近20日已跌-19.1%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=28.9超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面59.0 / 综合73.0</t>
+          <t>基本面82.0 / 技术面65.0 / 综合73.5</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.9中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.9中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -629,43 +629,43 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>54.46</t>
+          <t>301.00</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>6.19</v>
+        <v>16.39</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.98</v>
+        <v>3.73</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=42.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=21.4超卖区；近20日已跌-20.6%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面60.0 / 综合71.0</t>
+          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
         </is>
       </c>
     </row>
@@ -702,18 +702,18 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>54.37</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>23.85</v>
+        <v>23.65</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.0分（基本面84.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=43.4中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.5中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面56.0 / 综合70.0</t>
+          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
         </is>
       </c>
     </row>
@@ -760,14 +760,14 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.82</t>
+          <t>40.60</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6.79</v>
+        <v>6.75</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=49.5中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=45.2中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -803,43 +803,43 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>28.02</t>
+          <t>82.47</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>18.94</v>
+        <v>14.18</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3.17</v>
+        <v>2.97</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分62.5分（基本面78.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=34.5超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.5超卖区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面47.0 / 综合62.5</t>
+          <t>基本面75.0 / 技术面51.0 / 综合63.0</t>
         </is>
       </c>
     </row>
@@ -876,14 +876,14 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1253.80</t>
+          <t>1251.24</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.25</v>
+        <v>19.21</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6.24</v>
+        <v>6.23</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=33.8超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.5超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.61</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=45.0中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,43 +513,39 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>有色金属</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>53.87</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>6.12</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.97</v>
-      </c>
+          <t>30.01</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.5分（基本面82.0/技术面65.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分75.0分（基本面100/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=28.9超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=30.6超卖区；近20日已跌-13.2%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,50 +560,46 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面65.0 / 综合73.5</t>
+          <t>基本面100 / 技术面50.0 / 综合75.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>31.41</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>12.35</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>4.32</v>
-      </c>
+          <t>53.25</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.5分（基本面82.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=36.9中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=24.4超卖区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,7 +614,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面46.0 / 综合73.0</t>
+          <t>基本面82.0 / 技术面61.0 / 综合71.5</t>
         </is>
       </c>
     </row>
@@ -644,15 +636,11 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>301.00</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>16.39</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.73</v>
-      </c>
+          <t>293.50</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -665,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=21.4超卖区；近20日已跌-20.6%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.4超卖区；近20日已跌-21.3%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -687,48 +675,44 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>54.37</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>23.65</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.52</v>
-      </c>
+          <t>28.36</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.5中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=48.7中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
+          <t>基本面78.0 / 技术面60.0 / 综合69.0</t>
         </is>
       </c>
     </row>
@@ -760,15 +744,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.60</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.89</v>
-      </c>
+          <t>40.69</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -781,7 +761,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=45.2中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=38.6中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -818,15 +798,11 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82.47</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>14.18</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2.97</v>
-      </c>
+          <t>82.65</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -839,7 +815,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.5超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.8超卖区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -861,48 +837,44 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1251.24</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>6.23</v>
-      </c>
+          <t>52.00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分62.0分（基本面73.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分63.0分（基本面84.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.5超卖区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=43.2中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +884,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面51.0 / 综合62.0</t>
+          <t>基本面84.0 / 技术面42.0 / 综合63.0</t>
         </is>
       </c>
     </row>
@@ -934,7 +906,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.59</t>
+          <t>4.51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +921,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分53.0分（基本面60.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分51.0分（基本面60.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=45.0中性区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=36.7中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +946,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面46.0 / 综合53.0</t>
+          <t>基本面60.0 / 技术面42.0 / 综合51.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>30.01</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>11.79</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.13</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分75.0分（基本面100/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>53.25</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分71.5分（基本面82.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>293.50</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>15.98</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.64</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>28.36</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>19.17</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.21</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>40.69</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>82.65</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>14.21</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>2.98</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>52.00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>22.61</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4.32</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分63.0分（基本面84.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>30.01</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.13</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分75.0分（基本面100/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>53.25</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分71.5分（基本面82.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>293.50</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.64</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>28.36</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.21</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>40.69</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>82.65</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2.98</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>52.00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>4.32</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分63.0分（基本面84.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,15 +528,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>30.01</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>11.79</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.13</v>
-      </c>
+          <t>29.42</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分75.0分（基本面100/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -549,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=30.6超卖区；近20日已跌-13.2%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=30.2超卖区；近20日已跌-15.1%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -571,43 +567,39 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>53.25</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>6.05</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.95</v>
-      </c>
+          <t>28.55</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.5分（基本面82.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分74.0分（基本面78.0/技术面70.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=24.4超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD金叉；MACD红柱放大；RSI=68.2中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,7 +614,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面61.0 / 综合71.5</t>
+          <t>基本面78.0 / 技术面70.0 / 综合74.0</t>
         </is>
       </c>
     </row>
@@ -644,15 +636,11 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>293.50</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>15.98</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.64</v>
-      </c>
+          <t>291.99</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -665,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.4超卖区；近20日已跌-21.3%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.6超卖区；近20日已跌-20.8%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -687,43 +675,39 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28.36</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>19.17</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.21</v>
-      </c>
+          <t>52.40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=48.7中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.1超卖区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面60.0 / 综合69.0</t>
+          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
         </is>
       </c>
     </row>
@@ -760,15 +744,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.69</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>6.76</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9</v>
-      </c>
+          <t>40.64</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -781,7 +761,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=38.6中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=44.4中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -818,15 +798,11 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82.65</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>14.21</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>2.98</v>
-      </c>
+          <t>82.00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -839,7 +815,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.8超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.4超卖区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -861,48 +837,44 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52.00</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>22.61</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>4.32</v>
-      </c>
+          <t>1243.88</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分63.0分（基本面84.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分62.0分（基本面73.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=43.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.8超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,29 +884,29 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面42.0 / 综合63.0</t>
+          <t>基本面73.0 / 技术面51.0 / 综合62.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>宽基指数</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.51</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -959,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=36.7中性区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=41.8中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.42</t>
+          <t>29.55</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分75.0分（基本面100/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分77.0分（基本面100/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=30.2超卖区；近20日已跌-15.1%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=22.6超卖区；近20日已跌-12.2%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,46 +560,46 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面50.0 / 综合75.0</t>
+          <t>基本面100 / 技术面54.0 / 综合77.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.55</t>
+          <t>286.80</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分74.0分（基本面78.0/技术面70.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD金叉；MACD红柱放大；RSI=68.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.3超卖区；近20日已跌-21.1%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -614,46 +614,46 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面70.0 / 综合74.0</t>
+          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>291.99</t>
+          <t>28.45</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.6超卖区；近20日已跌-20.8%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=64.5中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,51 +668,51 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
+          <t>基本面78.0 / 技术面60.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52.40</t>
+          <t>50.40</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面84.0/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.1超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=36.3中性区；近20日已跌-12.5%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,46 +722,46 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
+          <t>基本面84.0 / 技术面45.0 / 综合64.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>52.57</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=44.4中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=33.0超卖区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -776,46 +776,46 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
+          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>82.00</t>
+          <t>40.51</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.4超卖区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=44.8中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -830,51 +830,51 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面51.0 / 综合63.0</t>
+          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1243.88</t>
+          <t>81.67</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分62.0分（基本面73.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.8超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.7超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -884,29 +884,29 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面51.0 / 综合62.0</t>
+          <t>基本面75.0 / 技术面51.0 / 综合63.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>588000</t>
+          <t>510300</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>科创50ETF</t>
+          <t>沪深300ETF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>宽基指数</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -921,7 +921,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分51.0分（基本面60.0/技术面42.0），技术面趋势偏弱，回避或减仓; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分53.5分（基本面60.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；RSI=41.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=29.0超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面42.0 / 综合51.0</t>
+          <t>基本面60.0 / 技术面47.0 / 综合53.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.55</t>
+          <t>29.46</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分77.0分（基本面100/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分75.0分（基本面100/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=22.6超卖区；近20日已跌-12.2%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=21.7超卖区；近20日已跌-12.5%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,7 +560,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面54.0 / 综合77.0</t>
+          <t>基本面100 / 技术面50.0 / 综合75.0</t>
         </is>
       </c>
     </row>
@@ -636,7 +636,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>28.38</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
@@ -653,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=64.5中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=62.3中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52.57</t>
+          <t>52.50</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
@@ -761,7 +761,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=33.0超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.2超卖区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81.67</t>
+          <t>81.66</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
@@ -906,7 +906,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=29.0超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=26.9超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.46</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+          <t>29.79</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.1</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分75.0分（基本面100/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=21.7超卖区；近20日已跌-12.5%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.6超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,46 +564,50 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面50.0 / 综合75.0</t>
+          <t>基本面100 / 技术面51.0 / 综合75.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>286.80</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+          <t>53.29</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.96</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.5分（基本面82.0/技术面65.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.3超卖区；近20日已跌-21.1%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=34.6超卖区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -614,7 +622,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
+          <t>基本面82.0 / 技术面65.0 / 综合73.5</t>
         </is>
       </c>
     </row>
@@ -636,14 +644,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.38</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t>28.54</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.23</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面78.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -653,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=62.3中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.0中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,51 +680,55 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面60.0 / 综合69.0</t>
+          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>50.40</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+          <t>291.11</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.61</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面84.0/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=36.3中性区；近20日已跌-12.5%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.1超卖区；近20日已跌-18.7%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,51 +738,55 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面45.0 / 综合64.5</t>
+          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52.50</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>49.43</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>4.11</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.2超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=31.3超卖区；近20日已跌-13.2%，接近超跌</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,7 +796,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
+          <t>基本面84.0 / 技术面50.0 / 综合67.0</t>
         </is>
       </c>
     </row>
@@ -798,14 +818,18 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>40.51</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+          <t>41.26</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.91</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -815,7 +839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=44.8中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=52.9中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -830,7 +854,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
+          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
         </is>
       </c>
     </row>
@@ -852,14 +876,18 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81.66</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+          <t>80.10</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2.89</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分61.0分（基本面75.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -869,7 +897,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.7超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=25.5超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -884,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面51.0 / 综合63.0</t>
+          <t>基本面75.0 / 技术面47.0 / 综合61.0</t>
         </is>
       </c>
     </row>
@@ -906,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.42</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -931,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=26.9超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=27.4超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>29.79</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.1</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>53.29</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>6.06</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.96</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.5分（基本面82.0/技术面65.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>28.54</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.23</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>291.11</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>15.85</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.61</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>49.43</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>21.5</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>4.11</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>41.26</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>6.86</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.91</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>80.10</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>13.77</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>2.89</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分61.0分（基本面75.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>29.79</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.1</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>53.29</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.96</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.5分（基本面82.0/技术面65.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>28.54</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>19.29</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.23</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>291.11</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>15.85</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.61</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>49.43</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>4.11</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>41.26</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.91</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>80.10</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2.89</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分61.0分（基本面75.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,11 +528,15 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.79</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+          <t>29.37</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.04</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -545,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.6超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.2超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -567,39 +571,43 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>53.29</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+          <t>28.90</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>19.53</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.27</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.5分（基本面82.0/技术面65.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=34.6超卖区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=67.1中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -614,46 +622,50 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面65.0 / 综合73.5</t>
+          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.54</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t>286.75</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>15.61</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.56</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.0中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.9超卖区；近20日已跌-17.7%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,51 +680,55 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
+          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>291.11</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+          <t>48.43</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>21.07</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4.03</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.1超卖区；近20日已跌-18.7%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.1超卖区；近20日已跌-15.2%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,51 +738,55 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
+          <t>基本面84.0 / 技术面50.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49.43</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>52.67</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>5.99</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.5分（基本面82.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=31.3超卖区；近20日已跌-13.2%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=29.2超卖区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -776,7 +796,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面50.0 / 综合67.0</t>
+          <t>基本面82.0 / 技术面51.0 / 综合66.5</t>
         </is>
       </c>
     </row>
@@ -798,11 +818,15 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.26</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+          <t>41.71</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.92</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -815,7 +839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=52.9中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=51.6中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -852,14 +876,18 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>80.10</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+          <t>81.74</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2.94</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分61.0分（基本面75.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -869,7 +897,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=25.5超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=33.5超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -884,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面47.0 / 综合61.0</t>
+          <t>基本面75.0 / 技术面51.0 / 综合63.0</t>
         </is>
       </c>
     </row>
@@ -906,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.43</t>
+          <t>4.39</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -931,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=27.4超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=26.1超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,43 +513,39 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.37</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>11.54</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.04</v>
-      </c>
+          <t>297.64</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分75.5分（基本面87.0/技术面64.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.2超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=32.0超卖区；近20日已跌-14.8%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,50 +560,46 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面51.0 / 综合75.5</t>
+          <t>基本面87.0 / 技术面64.0 / 综合75.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>有色金属</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.90</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>19.53</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.27</v>
-      </c>
+          <t>30.83</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=67.1中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.2中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,50 +614,46 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
+          <t>基本面100 / 技术面46.0 / 综合73.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>286.75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>15.61</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.56</v>
-      </c>
+          <t>28.98</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.9超卖区；近20日已跌-17.7%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.7中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,7 +668,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
+          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
         </is>
       </c>
     </row>
@@ -702,15 +690,11 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48.43</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>21.07</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.03</v>
-      </c>
+          <t>47.59</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -723,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.1超卖区；近20日已跌-15.2%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=26.6超卖区；近20日已跌-15.3%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -745,43 +729,39 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52.67</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+          <t>41.42</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面82.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=29.2超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=50.8中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +776,51 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面51.0 / 综合66.5</t>
+          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.71</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6.93</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.92</v>
-      </c>
+          <t>1263.00</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=51.6中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.6中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,50 +830,46 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>81.74</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>14.05</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>2.94</v>
-      </c>
+          <t>52.94</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分63.0分（基本面75.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=33.5超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.3中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -912,7 +884,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面51.0 / 综合63.0</t>
+          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
         </is>
       </c>
     </row>
@@ -949,7 +921,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分53.5分（基本面60.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分55.5分（基本面60.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=26.1超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=28.8超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +946,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面47.0 / 综合53.5</t>
+          <t>基本面60.0 / 技术面51.0 / 综合55.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,11 +528,15 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>297.64</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+          <t>297.75</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3.69</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面87.0/技术面64.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -545,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=32.0超卖区；近20日已跌-14.8%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=32.1超卖区；近20日已跌-14.8%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -582,11 +586,15 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>30.83</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+          <t>30.80</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>4.24</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -599,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.0中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -636,11 +644,15 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.98</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t>28.99</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.28</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -653,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.7中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.9中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -693,8 +705,12 @@
           <t>47.59</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.96</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -729,39 +745,43 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>41.42</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>52.83</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.5分（基本面82.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=50.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.2超卖区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -776,51 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面82.0 / 技术面51.0 / 综合66.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1263.00</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+          <t>41.42</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.91</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.6中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=50.8中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,51 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
+          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52.94</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+          <t>1263.00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>6.28</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.3中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.6中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -884,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
+          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
         </is>
       </c>
     </row>
@@ -906,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.39</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -921,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分55.5分（基本面60.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分53.5分（基本面60.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -931,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=28.8超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.1超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -946,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面51.0 / 综合55.5</t>
+          <t>基本面60.0 / 技术面47.0 / 综合53.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>297.75</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>16.21</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>3.69</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面87.0/技术面64.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>30.80</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>12.11</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>4.24</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>19.59</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.28</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>47.59</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>20.7</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.96</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>52.83</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面82.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>41.42</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.91</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>1263.00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>19.39</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>6.28</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>297.75</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>16.21</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3.69</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面87.0/技术面64.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>30.80</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>12.11</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>4.24</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>28.99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>19.59</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.28</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>47.59</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>20.7</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.96</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>52.83</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面82.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>41.42</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.91</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>1263.00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>6.28</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>297.75</t>
+          <t>42.76</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>16.21</v>
+        <v>7.11</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.69</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分75.5分（基本面87.0/技术面64.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分74.0分（基本面72.0/技术面76.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=32.1超卖区；近20日已跌-14.8%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD金叉；MACD红柱放大；RSI=58.9中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面64.0 / 综合75.5</t>
+          <t>基本面72.0 / 技术面76.0 / 综合74.0</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>30.80</t>
+          <t>30.22</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>12.11</v>
+        <v>11.88</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.24</v>
+        <v>4.16</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.0中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=37.1中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -644,14 +644,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.99</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19.59</v>
+        <v>19.86</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.28</v>
+        <v>3.33</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=62.9中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=66.2中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -687,48 +687,48 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47.59</t>
+          <t>53.24</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>20.7</v>
+        <v>6.05</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.96</v>
+        <v>0.95</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=26.6超卖区；近20日已跌-15.3%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=38.8中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -738,50 +738,50 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面50.0 / 综合67.0</t>
+          <t>基本面82.0 / 技术面60.0 / 综合71.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>52.83</t>
+          <t>298.38</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>6</v>
+        <v>16.24</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.95</v>
+        <v>3.7</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面82.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=34.2超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=27.4超卖区；近20日已跌-15.0%，接近超跌</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面51.0 / 综合66.5</t>
+          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.42</t>
+          <t>46.32</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.89</v>
+        <v>20.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.91</v>
+        <v>3.85</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=50.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=29.0超卖区；近20日已跌-14.7%，接近超跌</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面84.0 / 技术面50.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1263.00</t>
+          <t>83.50</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.39</v>
+        <v>14.36</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6.28</v>
+        <v>3.01</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分60.5分（基本面75.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.6中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=38.8中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
+          <t>基本面75.0 / 技术面46.0 / 综合60.5</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.1超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.2超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>有色金属</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>30.40</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.11</v>
+        <v>11.95</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.18</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分74.0分（基本面72.0/技术面76.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD金叉；MACD红柱放大；RSI=58.9中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=41.4中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,50 +564,50 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面76.0 / 综合74.0</t>
+          <t>基本面100 / 技术面46.0 / 综合73.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>30.22</t>
+          <t>29.15</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11.88</v>
+        <v>19.7</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>4.16</v>
+        <v>3.3</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=37.1中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=63.5中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,50 +622,50 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面46.0 / 综合73.0</t>
+          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>289.10</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19.86</v>
+        <v>15.74</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.33</v>
+        <v>3.59</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=66.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.6超卖区；近20日已跌-17.0%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
+          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>53.24</t>
+          <t>42.80</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>6.05</v>
+        <v>7.12</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.95</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=38.8中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=68.7中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,55 +738,55 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面60.0 / 综合71.0</t>
+          <t>基本面72.0 / 技术面66.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>298.38</t>
+          <t>46.15</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>16.24</v>
+        <v>20.08</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=27.4超卖区；近20日已跌-15.0%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=30.9超卖区；近20日已跌-17.5%，接近超跌</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
+          <t>基本面84.0 / 技术面50.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46.32</t>
+          <t>51.69</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>20.15</v>
+        <v>5.88</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3.85</v>
+        <v>0.93</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=29.0超卖区；近20日已跌-14.7%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=35.0超卖区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面50.0 / 综合67.0</t>
+          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
         </is>
       </c>
     </row>
@@ -876,14 +876,14 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>83.50</t>
+          <t>82.79</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>14.36</v>
+        <v>14.23</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>3.01</v>
+        <v>2.98</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=38.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.2中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.36</t>
+          <t>4.34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分53.5分（基本面60.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分55.5分（基本面60.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.2超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=29.1超卖区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面47.0 / 综合53.5</t>
+          <t>基本面60.0 / 技术面51.0 / 综合55.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,15 +528,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>30.40</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>11.95</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.18</v>
-      </c>
+          <t>29.98</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -549,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=41.4中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.2中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -586,15 +582,11 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>29.15</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>19.7</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.3</v>
-      </c>
+          <t>29.45</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -607,7 +599,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=63.5中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=68.5中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -629,43 +621,39 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>289.10</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>15.74</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.59</v>
-      </c>
+          <t>42.67</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.5分（基本面87.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.6超卖区；近20日已跌-17.0%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=69.5中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +668,46 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面54.0 / 综合70.5</t>
+          <t>基本面72.0 / 技术面66.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42.80</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+          <t>280.12</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=68.7中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.5超卖区；近20日已跌-16.5%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面66.0 / 综合69.0</t>
+          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
         </is>
       </c>
     </row>
@@ -760,15 +744,11 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>46.15</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>20.08</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3.84</v>
-      </c>
+          <t>44.94</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -781,7 +761,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=30.9超卖区；近20日已跌-17.5%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=22.3超卖区；近20日已跌-18.4%，接近超跌</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -803,43 +783,39 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51.69</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>5.88</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.93</v>
-      </c>
+          <t>83.70</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=35.0超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=45.2中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -854,50 +830,46 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
+          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82.79</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>14.23</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>2.98</v>
-      </c>
+          <t>51.23</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分60.5分（基本面75.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=34.6超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -912,29 +884,29 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面46.0 / 综合60.5</t>
+          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>宽基指数</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.34</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +921,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分55.5分（基本面60.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分55.0分（基本面60.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=29.1超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=19.7超卖区；近20日已跌-13.3%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +946,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面51.0 / 综合55.5</t>
+          <t>基本面60.0 / 技术面50.0 / 综合55.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>29.98</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.12</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>29.45</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.33</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>42.67</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>280.12</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>15.25</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.48</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>44.94</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>19.55</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.77</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>83.70</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.02</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>51.23</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.92</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,18 +528,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.98</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11.78</v>
+        <v>11.55</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.5分（基本面100/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=35.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=38.7中性区；近20日已跌-14.6%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面46.0 / 综合73.0</t>
+          <t>基本面100 / 技术面45.0 / 综合72.5</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.60</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>19.9</v>
+        <v>20.01</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=68.5中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=70.2中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -629,43 +629,43 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42.67</t>
+          <t>278.50</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7.09</v>
+        <v>15.16</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.46</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.0分（基本面87.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=69.5中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.3超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-17.3%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,55 +680,55 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面66.0 / 综合69.0</t>
+          <t>基本面87.0 / 技术面55.0 / 综合71.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>280.12</t>
+          <t>44.65</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>15.25</v>
+        <v>19.43</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.48</v>
+        <v>3.75</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面84.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.5超卖区；近20日已跌-16.5%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.0超卖区；近20日已跌-20.1%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -738,55 +738,55 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
+          <t>基本面84.0 / 技术面54.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>44.94</t>
+          <t>42.66</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.55</v>
+        <v>7.09</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.77</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面84.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=22.3超卖区；近20日已跌-18.4%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.6中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面50.0 / 综合67.0</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83.70</t>
+          <t>1312.97</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.39</v>
+        <v>20.16</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3.02</v>
+        <v>6.53</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=45.2中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=64.7中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
+          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
         </is>
       </c>
     </row>
@@ -876,18 +876,18 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.23</t>
+          <t>51.78</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.82</v>
+        <v>5.89</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=34.6超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.9中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
+          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分55.0分（基本面60.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分57.5分（基本面60.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=19.7超卖区；近20日已跌-13.3%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=19.3超卖区；5日均量为60日均量的1.31倍，量能放大；近20日已跌-13.9%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面50.0 / 综合55.0</t>
+          <t>基本面60.0 / 技术面55.0 / 综合57.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -879,12 +879,8 @@
           <t>51.78</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>5.89</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -879,8 +879,12 @@
           <t>51.78</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>5.89</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.93</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,18 +528,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.38</t>
+          <t>29.92</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11.55</v>
+        <v>11.76</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>4.04</v>
+        <v>4.11</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.5分（基本面100/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分74.5分（基本面100/技术面49.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=38.7中性区；近20日已跌-14.6%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.0中性区；近20日已跌-12.3%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面45.0 / 综合72.5</t>
+          <t>基本面100 / 技术面49.0 / 综合74.5</t>
         </is>
       </c>
     </row>
@@ -586,18 +586,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>29.60</t>
+          <t>29.38</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>20.01</v>
+        <v>19.86</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=70.2中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=69.5中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,55 +622,55 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
+          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>278.50</t>
+          <t>44.67</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>15.16</v>
+        <v>19.43</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.46</v>
+        <v>3.75</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面87.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面84.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.3超卖区；5日均量为60日均量的1.32倍，量能放大；近20日已跌-17.3%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=10.4超卖区；近20日已跌-18.0%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -680,55 +680,55 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面55.0 / 综合71.0</t>
+          <t>基本面84.0 / 技术面54.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>44.65</t>
+          <t>277.00</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>19.43</v>
+        <v>15.08</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.75</v>
+        <v>3.44</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面84.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=23.0超卖区；近20日已跌-20.1%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.6超卖区；近20日已跌-18.1%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面54.0 / 综合69.0</t>
+          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
         </is>
       </c>
     </row>
@@ -760,14 +760,14 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>42.45</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7.09</v>
+        <v>7.06</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -781,7 +781,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.6中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=71.2中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -818,14 +818,14 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1312.97</t>
+          <t>1329.00</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>20.16</v>
+        <v>20.4</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>6.53</v>
+        <v>6.61</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=64.7中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=72.0中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -876,11 +876,11 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.78</t>
+          <t>51.88</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>0.93</v>
@@ -897,7 +897,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.9中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.6中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分57.5分（基本面60.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分57.0分（基本面60.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=19.3超卖区；5日均量为60日均量的1.31倍，量能放大；近20日已跌-13.9%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.7超卖区；近20日已跌-13.8%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面55.0 / 综合57.5</t>
+          <t>基本面60.0 / 技术面54.0 / 综合57.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>29.92</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.11</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分74.5分（基本面100/技术面49.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>29.38</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>19.86</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.33</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>44.67</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>19.43</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.75</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面84.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>277.00</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>15.08</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.44</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>42.45</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>7.06</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>1329.00</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>20.4</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>6.61</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>51.88</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,18 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.92</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+          <t>29.79</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.1</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分74.5分（基本面100/技术面49.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.0中性区；近20日已跌-12.3%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=38.8中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,46 +564,50 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面49.0 / 综合74.5</t>
+          <t>基本面100 / 技术面46.0 / 综合73.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>29.38</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+          <t>43.05</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=69.5中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.2中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -614,7 +622,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
+          <t>基本面72.0 / 技术面66.0 / 综合69.0</t>
         </is>
       </c>
     </row>
@@ -636,11 +644,15 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44.67</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t>46.20</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.88</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面84.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -653,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=10.4超卖区；近20日已跌-18.0%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.5超卖区；近20日已跌-16.6%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -690,11 +702,15 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>277.00</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+          <t>267.02</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.31</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -707,7 +723,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=32.6超卖区；近20日已跌-18.1%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=30.5超卖区；近20日已跌-19.2%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -729,39 +745,43 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.45</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>86.54</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.12</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=71.2中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=72.5中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -776,51 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
+          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1329.00</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+          <t>29.54</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.34</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=72.0中性区</t>
+          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.4超买区，短期回调风险</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,51 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
+          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.88</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+          <t>1324.97</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>6.59</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=40.6中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=72.3中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -884,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
+          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
         </is>
       </c>
     </row>
@@ -906,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -921,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分57.0分（基本面60.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分59.5分（基本面60.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -931,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.7超卖区；近20日已跌-13.8%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=7.0超卖区；5日均量为60日均量的1.33倍，量能放大；近20日已跌-14.3%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -946,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面54.0 / 综合57.0</t>
+          <t>基本面60.0 / 技术面59.0 / 综合59.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>29.79</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>11.71</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.1</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>43.05</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>7.16</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>46.20</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>20.1</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.88</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面84.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>267.02</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.31</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>86.54</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>14.88</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3.12</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>29.54</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>19.97</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>3.34</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>1324.97</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>20.34</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>6.59</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>29.79</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4.1</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>43.05</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>46.20</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.88</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面84.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>267.02</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.31</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>86.54</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.12</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>29.54</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>19.97</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.34</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>1324.97</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>6.59</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>29.06</t>
         </is>
       </c>
       <c r="E2" s="2" t="n"/>
       <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.5分（基本面100/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -545,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=38.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=34.1超卖区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,46 +560,46 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面46.0 / 综合73.0</t>
+          <t>基本面100 / 技术面47.0 / 综合73.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>43.05</t>
+          <t>85.28</t>
         </is>
       </c>
       <c r="E3" s="2" t="n"/>
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面72.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.2中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=61.3中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -614,7 +614,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面66.0 / 综合69.0</t>
+          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
         </is>
       </c>
     </row>
@@ -636,14 +636,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>46.20</t>
+          <t>47.60</t>
         </is>
       </c>
       <c r="E4" s="2" t="n"/>
       <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面84.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面84.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -653,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=18.5超卖区；近20日已跌-16.6%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=24.3超卖区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,46 +668,46 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面54.0 / 综合69.0</t>
+          <t>基本面84.0 / 技术面51.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>267.02</t>
+          <t>42.52</t>
         </is>
       </c>
       <c r="E5" s="2" t="n"/>
       <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=12.08%，盈利能力良好；营收同比+54.80%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=30.5超卖区；近20日已跌-19.2%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -722,46 +722,46 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86.54</t>
+          <t>29.69</t>
         </is>
       </c>
       <c r="E6" s="2" t="n"/>
       <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=72.5中性区</t>
+          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=78.7超买区，短期回调风险</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -776,51 +776,51 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
+          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>1331.88</t>
         </is>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.4超买区，短期回调风险</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=73.2中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -830,51 +830,51 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
+          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1324.97</t>
+          <t>51.20</t>
         </is>
       </c>
       <c r="E8" s="2" t="n"/>
       <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=72.3中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.2超卖区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -884,7 +884,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
+          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
         </is>
       </c>
     </row>
@@ -906,7 +906,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=7.0超卖区；5日均量为60日均量的1.33倍，量能放大；近20日已跌-14.3%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=7.7超卖区；5日均量为60日均量的1.44倍，量能放大；近20日已跌-12.2%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>11.42</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分73.5分（基本面100/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>85.28</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>14.66</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.07</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>47.60</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>20.71</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面84.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>42.52</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>29.69</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.36</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>1331.88</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>20.45</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>6.63</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>51.20</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.92</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>29.06</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>11.42</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分73.5分（基本面100/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>85.28</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>14.66</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.07</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>47.60</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>20.71</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>4</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面84.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -687,43 +675,39 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>7.07</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+          <t>259.08</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面94.0/技术面40.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
+          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；MACD死叉；RSI=20.6超卖区；近20日已跌-23.1%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,50 +722,46 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
+          <t>基本面94.0 / 技术面40.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29.69</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>20.07</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3.36</v>
-      </c>
+          <t>42.52</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=78.7超买区，短期回调风险</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +776,51 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1331.88</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>20.45</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>6.63</v>
-      </c>
+          <t>29.69</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=73.2中性区</t>
+          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=78.7超买区，短期回调风险</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +830,51 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
+          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>51.20</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.92</v>
-      </c>
+          <t>1331.88</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面82.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=28.2超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=73.2中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +884,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面47.0 / 综合64.5</t>
+          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,39 +513,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>29.06</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+          <t>227.90</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>12.02</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2.73</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.5分（基本面100/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分74.5分（基本面94.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=34.1超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=15.2超卖区；5日均量为60日均量的1.77倍，量能放大；近20日已跌-28.0%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -560,46 +564,50 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面47.0 / 综合73.5</t>
+          <t>基本面94.0 / 技术面55.0 / 综合74.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>有色金属</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>85.28</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+          <t>28.87</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>11.35</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.97</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.5分（基本面100/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=61.3中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=33.2超卖区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -614,7 +622,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
+          <t>基本面100 / 技术面47.0 / 综合73.5</t>
         </is>
       </c>
     </row>
@@ -636,14 +644,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>47.60</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t>48.09</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>20.92</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4.04</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面84.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.5分（基本面84.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -653,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=24.3超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=27.8超卖区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -668,46 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面51.0 / 综合67.5</t>
+          <t>基本面84.0 / 技术面61.0 / 综合72.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>259.08</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+          <t>42.28</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>7.03</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.93</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面94.0/技术面40.0），技术面趋势偏弱，回避或减仓; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势偏弱，回避或减仓。价格位于60日均线下方，中期趋势偏弱；MACD死叉；RSI=20.6超卖区；近20日已跌-23.1%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.3中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -722,46 +738,50 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面94.0 / 技术面40.0 / 综合67.0</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.52</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>29.57</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>19.99</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.35</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
+          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.1超买区，短期回调风险</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -776,46 +796,50 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
+          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>29.69</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+          <t>51.20</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.92</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.5分（基本面82.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=78.7超买区，短期回调风险</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.6超卖区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -830,7 +854,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
+          <t>基本面82.0 / 技术面51.0 / 综合66.5</t>
         </is>
       </c>
     </row>
@@ -852,14 +876,18 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1331.88</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+          <t>1309.69</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>6.52</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -869,7 +897,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=73.2中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=65.6中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -884,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
+          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
         </is>
       </c>
     </row>
@@ -931,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=7.7超卖区；5日均量为60日均量的1.44倍，量能放大；近20日已跌-12.2%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.0超卖区；5日均量为60日均量的1.51倍，量能放大；近20日已跌-13.4%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>有色金属</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>227.90</t>
+          <t>27.84</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.02</v>
+        <v>10.94</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.73</v>
+        <v>3.83</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分74.5分（基本面94.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分75.0分（基本面100/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=15.2超卖区；5日均量为60日均量的1.77倍，量能放大；近20日已跌-28.0%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=35.0超卖区；近20日已跌-13.5%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,50 +564,50 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面94.0 / 技术面55.0 / 综合74.5</t>
+          <t>基本面100 / 技术面50.0 / 综合75.0</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.87</t>
+          <t>220.41</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11.35</v>
+        <v>11.63</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.97</v>
+        <v>2.64</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.5分（基本面100/技术面47.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分74.5分（基本面94.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=33.2超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=15.2超卖区；5日均量为60日均量的2.01倍，量能放大；近20日已跌-27.8%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,55 +622,55 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面47.0 / 综合73.5</t>
+          <t>基本面94.0 / 技术面55.0 / 综合74.5</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600900</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>长江电力</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>电力</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48.09</t>
+          <t>29.82</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20.92</v>
+        <v>20.15</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>4.04</v>
+        <v>3.38</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.5分（基本面84.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=27.8超卖区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.8中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面61.0 / 综合72.5</t>
+          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42.28</t>
+          <t>85.29</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7.03</v>
+        <v>14.66</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.93</v>
+        <v>3.07</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.3中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=59.0中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,55 +738,55 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
+          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29.57</t>
+          <t>47.01</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.99</v>
+        <v>20.45</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面78.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面84.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.1超买区，短期回调风险</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.8超卖区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面56.0 / 综合67.0</t>
+          <t>基本面84.0 / 技术面51.0 / 综合67.5</t>
         </is>
       </c>
     </row>
@@ -818,14 +818,14 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51.20</t>
+          <t>50.94</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5.82</v>
+        <v>5.79</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.6超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.3超卖区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -876,14 +876,14 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1309.69</t>
+          <t>1318.49</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20.1</v>
+        <v>20.24</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6.52</v>
+        <v>6.56</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=65.6中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=72.3中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.0超卖区；5日均量为60日均量的1.51倍，量能放大；近20日已跌-13.4%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.0超卖区；5日均量为60日均量的1.49倍，量能放大；近20日已跌-19.4%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>601899</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>有色金属</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>237.60</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>10.94</v>
+        <v>12.54</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>3.83</v>
+        <v>2.84</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分75.0分（基本面100/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=19.60%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+15.78%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=35.0超卖区；近20日已跌-13.5%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=27.5超卖区；5日均量为60日均量的2.39倍，量能放大；近20日已跌-21.9%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,50 +564,50 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面50.0 / 综合75.0</t>
+          <t>基本面94.0 / 技术面59.0 / 综合76.5</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>601899</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>有色金属</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>220.41</t>
+          <t>28.79</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>11.63</v>
+        <v>11.32</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>2.64</v>
+        <v>3.96</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分74.5分（基本面94.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=28.30%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+11.51%，成长性较好</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=15.2超卖区；5日均量为60日均量的2.01倍，量能放大；近20日已跌-27.8%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=45.8中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面94.0 / 技术面55.0 / 综合74.5</t>
+          <t>基本面100 / 技术面46.0 / 综合73.0</t>
         </is>
       </c>
     </row>
@@ -644,14 +644,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.82</t>
+          <t>29.45</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20.15</v>
+        <v>19.9</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=74.8中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=64.4中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -702,14 +702,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85.29</t>
+          <t>85.59</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.66</v>
+        <v>14.72</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=59.0中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=62.5中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -745,48 +745,48 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>47.01</t>
+          <t>1335.00</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.45</v>
+        <v>20.49</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.95</v>
+        <v>6.64</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面84.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.8超卖区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=73.7中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面51.0 / 综合67.5</t>
+          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50.94</t>
+          <t>50.42</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>5.79</v>
+        <v>21.94</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.91</v>
+        <v>4.23</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面82.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=32.3超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=52.2中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面51.0 / 综合66.5</t>
+          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1318.49</t>
+          <t>41.77</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20.24</v>
+        <v>6.94</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6.56</v>
+        <v>0.92</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=72.3中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=60.8中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
+          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=8.0超卖区；5日均量为60日均量的1.49倍，量能放大；近20日已跌-19.4%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.5超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-16.2%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>237.60</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>12.54</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2.84</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>28.79</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>11.32</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.96</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>29.45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>19.9</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.33</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>85.59</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>3.08</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>1335.00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>20.49</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6.64</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>50.42</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>21.94</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>4.23</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>41.77</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>6.94</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>0.92</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>237.60</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>12.54</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2.84</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>28.79</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>10.72</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.67</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>29.45</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>19.9</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.33</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>85.59</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>14.72</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.08</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>1335.00</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>20.49</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>6.64</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>50.42</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>21.94</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>4.23</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>41.77</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.92</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>237.60</t>
+          <t>238.00</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.54</v>
+        <v>12.56</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=27.5超卖区；5日均量为60日均量的2.39倍，量能放大；近20日已跌-21.9%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=28.9超卖区；5日均量为60日均量的2.52倍，量能放大；近20日已跌-21.2%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -586,18 +586,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.79</t>
+          <t>27.47</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10.72</v>
+        <v>10.22</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.5分（基本面100/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=45.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=38.8中性区；近20日已跌-12.5%，接近超跌</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面46.0 / 综合73.0</t>
+          <t>基本面100 / 技术面45.0 / 综合72.5</t>
         </is>
       </c>
     </row>
@@ -644,18 +644,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.45</t>
+          <t>29.86</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>19.9</v>
+        <v>20.18</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=64.4中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.0中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
+          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>85.59</t>
+          <t>42.50</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>14.72</v>
+        <v>7.07</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>3.08</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=62.5中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=67.1中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,55 +738,55 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
+          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1335.00</t>
+          <t>85.50</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.49</v>
+        <v>14.7</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>6.64</v>
+        <v>3.08</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=73.7中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=63.6中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
+          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
         </is>
       </c>
     </row>
@@ -818,14 +818,14 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50.42</t>
+          <t>49.81</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21.94</v>
+        <v>21.67</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.23</v>
+        <v>4.18</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=52.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.3中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -861,43 +861,43 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>52.62</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>6.94</v>
+        <v>5.98</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.92</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面72.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=60.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=50.8中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面56.0 / 综合64.0</t>
+          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
         </is>
       </c>
     </row>
@@ -934,7 +934,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.5超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-16.2%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.7超卖区；5日均量为60日均量的1.78倍，量能放大；近20日已跌-20.8%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>238.00</t>
+          <t>233.00</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.56</v>
+        <v>12.29</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=28.9超卖区；5日均量为60日均量的2.52倍，量能放大；近20日已跌-21.2%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.1超卖区；5日均量为60日均量的2.42倍，量能放大；近20日已跌-21.6%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -586,18 +586,18 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>27.85</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10.22</v>
+        <v>10.37</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.5分（基本面100/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=38.8中性区；近20日已跌-12.5%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.1中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面45.0 / 综合72.5</t>
+          <t>基本面100 / 技术面46.0 / 综合73.0</t>
         </is>
       </c>
     </row>
@@ -644,18 +644,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>29.83</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20.18</v>
+        <v>20.16</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>3.38</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.0分（基本面78.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.0中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=70.0中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面66.0 / 综合72.0</t>
+          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>601318</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>保险</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>42.50</t>
+          <t>52.61</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>7.07</v>
+        <v>5.98</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=67.1中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.8中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,50 +738,50 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.50</t>
+          <t>42.99</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>14.7</v>
+        <v>7.15</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>3.08</v>
+        <v>0.95</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=63.6中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=65.5中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
+          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>49.81</t>
+          <t>85.04</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>21.67</v>
+        <v>14.62</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>4.18</v>
+        <v>3.06</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.3中性区</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=68.9中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
+          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>52.62</t>
+          <t>48.80</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5.98</v>
+        <v>21.23</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.1</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分64.0分（基本面82.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=50.8中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.2中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,29 +912,29 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面46.0 / 综合64.0</t>
+          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>588000</t>
+          <t>510300</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>科创50ETF</t>
+          <t>沪深300ETF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>宽基指数</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分59.5分（基本面60.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分58.0分（基本面60.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.7超卖区；5日均量为60日均量的1.78倍，量能放大；近20日已跌-20.8%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=16.5超卖区；5日均量为60日均量的2.33倍，量能放大</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面59.0 / 综合59.5</t>
+          <t>基本面60.0 / 技术面56.0 / 综合58.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>233.00</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2.79</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>27.85</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>10.37</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.55</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>29.83</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>20.16</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.38</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>52.61</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>42.99</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.95</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>85.04</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>14.62</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>3.06</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>48.80</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>21.23</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>4.1</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>233.00</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2.79</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>27.85</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.55</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>29.83</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>20.16</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.38</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>52.61</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>42.99</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>85.04</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.06</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>48.80</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>21.23</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4.1</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,14 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>233.00</t>
+          <t>229.14</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.29</v>
+        <v>12.09</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.79</v>
+        <v>2.74</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
@@ -549,7 +549,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.1超卖区；5日均量为60日均量的2.42倍，量能放大；近20日已跌-21.6%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.2超卖区；5日均量为60日均量的1.89倍，量能放大；近20日已跌-24.8%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -586,14 +586,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>27.85</t>
+          <t>27.95</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10.37</v>
+        <v>10.4</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=39.1中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=41.7中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -644,18 +644,18 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>29.40</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20.16</v>
+        <v>19.87</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.38</v>
+        <v>3.33</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.5分（基本面78.0/技术面67.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=70.0中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=57.6中性区；5日均量为60日均量的1.39倍，量能放大</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,50 +680,50 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面62.0 / 综合70.0</t>
+          <t>基本面78.0 / 技术面67.0 / 综合72.5</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>601318</t>
+          <t>600276</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>恒瑞医药</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>保险</t>
+          <t>医药</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>52.61</t>
+          <t>48.36</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5.98</v>
+        <v>36.13</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>0.9399999999999999</v>
+        <v>4.8</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面82.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.0分（基本面84.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=9.00%，盈利能力良好；营收同比+15.01%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=12.17%，盈利能力良好；营收同比+5.26%，保持正增长</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD金叉；MACD红柱放大；RSI=44.8中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=56.0中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,50 +738,50 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面56.0 / 综合69.0</t>
+          <t>基本面84.0 / 技术面60.0 / 综合72.0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.99</t>
+          <t>85.91</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7.15</v>
+        <v>14.77</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.95</v>
+        <v>3.1</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=65.5中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=67.0中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,50 +796,50 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85.04</t>
+          <t>42.13</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.62</v>
+        <v>7</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3.06</v>
+        <v>0.93</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分66.5分（基本面72.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=68.9中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=53.5中性区；5日均量为60日均量的1.34倍，量能放大</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
+          <t>基本面72.0 / 技术面61.0 / 综合66.5</t>
         </is>
       </c>
     </row>
@@ -876,14 +876,14 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>48.80</t>
+          <t>49.70</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>21.23</v>
+        <v>21.62</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4.1</v>
+        <v>4.17</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=48.2中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=54.9中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -919,22 +919,22 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>宽基指数</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.12</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分58.0分（基本面60.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分59.5分（基本面60.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=16.5超卖区；5日均量为60日均量的2.33倍，量能放大</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.7超卖区；5日均量为60日均量的1.80倍，量能放大；近20日已跌-23.0%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面56.0 / 综合58.0</t>
+          <t>基本面60.0 / 技术面59.0 / 综合59.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>229.14</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2.74</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>27.95</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.56</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>29.40</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>19.87</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.33</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分72.5分（基本面78.0/技术面67.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>48.36</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>36.13</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.8</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面84.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>85.91</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3.1</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>42.13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面72.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>49.70</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>4.17</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>229.14</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2.74</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>27.95</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.56</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>29.40</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>19.87</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.33</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分72.5分（基本面78.0/技术面67.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>48.36</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>36.13</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4.8</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面84.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>85.91</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>14.77</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.1</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>42.13</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.93</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分66.5分（基本面72.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>49.70</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4.17</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -528,15 +528,11 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>229.14</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>12.09</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>2.74</v>
-      </c>
+          <t>229.07</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -549,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.2超卖区；5日均量为60日均量的1.89倍，量能放大；近20日已跌-24.8%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.3超卖区；5日均量为60日均量的1.60倍，量能放大；近20日已跌-23.9%，接近超跌</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -586,18 +582,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>27.95</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.56</v>
-      </c>
+          <t>28.04</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分73.0分（基本面100/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -607,7 +599,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=41.7中性区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.9超卖区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,7 +614,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面46.0 / 综合73.0</t>
+          <t>基本面100 / 技术面51.0 / 综合75.5</t>
         </is>
       </c>
     </row>
@@ -644,18 +636,14 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>19.87</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.33</v>
-      </c>
+          <t>29.99</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分72.5分（基本面78.0/技术面67.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分74.5分（基本面78.0/技术面71.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -665,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=57.6中性区；5日均量为60日均量的1.39倍，量能放大</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=63.2中性区；5日均量为60日均量的1.37倍，量能放大</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,7 +668,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面67.0 / 综合72.5</t>
+          <t>基本面78.0 / 技术面71.0 / 综合74.5</t>
         </is>
       </c>
     </row>
@@ -702,15 +690,11 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48.36</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>36.13</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.8</v>
-      </c>
+          <t>48.62</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面84.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -723,7 +707,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=56.0中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=57.7中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -745,43 +729,39 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>85.91</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>14.77</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3.1</v>
-      </c>
+          <t>42.94</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.5分（基本面75.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.5分（基本面72.0/技术面71.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=67.0中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=61.7中性区；5日均量为60日均量的1.36倍，量能放大</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,50 +776,46 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面60.0 / 综合67.5</t>
+          <t>基本面72.0 / 技术面71.0 / 综合71.5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>42.13</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.93</v>
-      </c>
+          <t>87.48</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面72.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=18.06%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.20%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=53.5中性区；5日均量为60日均量的1.34倍，量能放大</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=69.1中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -854,55 +830,51 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面61.0 / 综合66.5</t>
+          <t>基本面82.0 / 技术面60.0 / 综合71.0</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>002475</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>消费电子</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>49.70</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>4.17</v>
-      </c>
+          <t>1354.00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.0分（基本面84.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面73.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=8.76%，盈利能力良好；营收同比+40.16%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=54.9中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=70.7中性区；5日均量为60日均量的1.31倍，量能放大</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>销售净利率=4.89%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,29 +884,29 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面84.0 / 技术面46.0 / 综合65.0</t>
+          <t>基本面73.0 / 技术面61.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>588000</t>
+          <t>510300</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>科创50ETF</t>
+          <t>沪深300ETF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>科技</t>
+          <t>宽基指数</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>4.11</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +921,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分59.5分（基本面60.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分58.0分（基本面60.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +931,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=25.7超卖区；5日均量为60日均量的1.80倍，量能放大；近20日已跌-23.0%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=21.7超卖区；5日均量为60日均量的2.00倍，量能放大</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +946,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面59.0 / 综合59.5</t>
+          <t>基本面60.0 / 技术面56.0 / 综合58.0</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>229.07</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>12.09</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>2.74</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -585,8 +589,12 @@
           <t>28.04</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+      <c r="E3" s="2" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.57</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -639,8 +647,12 @@
           <t>29.99</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+      <c r="E4" s="2" t="n">
+        <v>20.27</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>3.4</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分74.5分（基本面78.0/技术面71.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -693,8 +705,12 @@
           <t>48.62</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>36.33</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4.83</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面84.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -747,8 +763,12 @@
           <t>42.94</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+      <c r="E6" s="2" t="n">
+        <v>7.14</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.95</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分71.5分（基本面72.0/技术面71.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -801,8 +821,12 @@
           <t>87.48</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>1354.00</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>20.79</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>6.74</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分67.0分（基本面73.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -513,43 +513,43 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>300750</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>新能源电池</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>229.07</t>
+          <t>43.55</t>
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>12.09</v>
+        <v>7.18</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>2.74</v>
+        <v>0.93</v>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分76.5分（基本面94.0/技术面59.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分82.0分（基本面83.0/技术面81.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=10.12%，盈利能力良好；营收同比+5.34%，保持正增长</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=17.3超卖区；5日均量为60日均量的1.60倍，量能放大；近20日已跌-23.9%，接近超跌</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD金叉；MACD红柱放大；RSI=56.8中性区；5日均量为60日均量的1.32倍，量能放大</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面94.0 / 技术面59.0 / 综合76.5</t>
+          <t>基本面83.0 / 技术面81.0 / 综合82.0</t>
         </is>
       </c>
     </row>
@@ -586,14 +586,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>28.04</t>
+          <t>27.62</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>10.44</v>
+        <v>10.27</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>3.57</v>
+        <v>3.52</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
@@ -607,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=30.9超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.6超卖区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -629,43 +629,43 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>600900</t>
+          <t>300750</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>长江电力</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>新能源电池</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29.99</t>
+          <t>233.37</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>20.27</v>
+        <v>12.29</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>3.4</v>
+        <v>2.79</v>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>综合评分74.5分（基本面78.0/技术面71.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分74.0分（基本面94.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.55%，盈利能力一般；营收同比+3.36%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=17.64%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+56.19%，成长性较好</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=63.2中性区；5日均量为60日均量的1.37倍，量能放大</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.1超卖区；近20日已跌-20.5%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>基本面78.0 / 技术面71.0 / 综合74.5</t>
+          <t>基本面94.0 / 技术面54.0 / 综合74.0</t>
         </is>
       </c>
     </row>
@@ -702,14 +702,14 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>48.62</t>
+          <t>48.46</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>36.33</v>
+        <v>36.21</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4.83</v>
+        <v>4.81</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=57.7中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=61.2中性区</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -745,43 +745,43 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>42.94</t>
+          <t>89.11</t>
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>7.14</v>
+        <v>14.34</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>0.95</v>
+        <v>3.06</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.5分（基本面72.0/技术面71.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=18.06%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.20%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=61.7中性区；5日均量为60日均量的1.36倍，量能放大</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=70.5中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -796,55 +796,55 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面71.0 / 综合71.5</t>
+          <t>基本面82.0 / 技术面60.0 / 综合71.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87.48</t>
+          <t>1392.05</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>14.07</v>
+        <v>21.18</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>3</v>
+        <v>6.42</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分69.5分（基本面73.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=18.06%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.20%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=24.47%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.82%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=69.1中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=72.3中性区；5日均量为60日均量的1.34倍，量能放大；近20日已涨12.5%，短期涨幅过大</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-0.25%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -854,55 +854,55 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面60.0 / 综合71.0</t>
+          <t>基本面73.0 / 技术面66.0 / 综合69.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>002475</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>消费电子</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1354.00</t>
+          <t>45.60</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>20.79</v>
+        <v>19.47</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>6.74</v>
+        <v>2.96</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分67.0分（基本面73.0/技术面61.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面84.0/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=13.86%，盈利能力良好；营收同比+29.01%，成长性较好</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；RSI=70.7中性区；5日均量为60日均量的1.31倍，量能放大</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=48.1中性区；近20日已跌-12.1%，接近超跌</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>销售净利率=4.99%，盈利空间薄；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,29 +912,29 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面61.0 / 综合67.0</t>
+          <t>基本面84.0 / 技术面45.0 / 综合64.5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>510300</t>
+          <t>588000</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>沪深300ETF</t>
+          <t>科创50ETF</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>宽基指数</t>
+          <t>科技</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分58.0分（基本面60.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分57.5分（基本面60.0/技术面55.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=21.7超卖区；5日均量为60日均量的2.00倍，量能放大</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=20.1超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-28.2%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面56.0 / 综合58.0</t>
+          <t>基本面60.0 / 技术面55.0 / 综合57.5</t>
         </is>
       </c>
     </row>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分82.0分（基本面83.0/技术面81.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>27.62</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.52</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>233.37</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2.79</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分74.0分（基本面94.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>48.46</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>36.21</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.81</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面84.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>89.11</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3.06</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>1392.05</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>21.18</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>6.42</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分69.5分（基本面73.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>45.60</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>19.47</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>2.96</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.5分（基本面84.0/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,8 +531,12 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n"/>
-      <c r="F2" s="2" t="n"/>
+      <c r="E2" s="2" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.93</v>
+      </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分82.0分（基本面83.0/技术面81.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -582,11 +586,15 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>27.62</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n"/>
-      <c r="F3" s="2" t="n"/>
+          <t>27.60</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.52</v>
+      </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -599,7 +607,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.6超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=31.5超卖区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -636,11 +644,15 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>233.37</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n"/>
-      <c r="F4" s="2" t="n"/>
+          <t>232.92</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>2.79</v>
+      </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分74.0分（基本面94.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -653,7 +665,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=20.1超卖区；近20日已跌-20.5%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=19.8超卖区；近20日已跌-20.6%，接近超跌</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -693,8 +705,12 @@
           <t>48.46</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
+      <c r="E5" s="2" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>4.81</v>
+      </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面84.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -744,11 +760,15 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>89.11</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n"/>
-      <c r="F6" s="2" t="n"/>
+          <t>89.18</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.06</v>
+      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -761,7 +781,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=70.5中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=70.6中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -801,8 +821,12 @@
           <t>1392.05</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n"/>
-      <c r="F7" s="2" t="n"/>
+      <c r="E7" s="2" t="n">
+        <v>21.18</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>6.42</v>
+      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分69.5分（基本面73.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -855,8 +879,12 @@
           <t>45.60</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n"/>
-      <c r="F8" s="2" t="n"/>
+      <c r="E8" s="2" t="n">
+        <v>19.47</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2.96</v>
+      </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.5分（基本面84.0/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -931,7 +959,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=20.1超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-28.2%，接近超跌</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=20.0超卖区；5日均量为60日均量的1.67倍，量能放大；近20日已跌-28.3%，接近超跌</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/outputs/03_候选股票池及初步分析表.xlsx
+++ b/outputs/03_候选股票池及初步分析表.xlsx
@@ -531,12 +531,8 @@
           <t>43.55</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
-        <v>7.18</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.93</v>
-      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>综合评分82.0分（基本面83.0/技术面81.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -589,12 +585,8 @@
           <t>27.60</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>10.27</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>3.52</v>
-      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
           <t>综合评分75.5分（基本面100/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -647,12 +639,8 @@
           <t>232.92</t>
         </is>
       </c>
-      <c r="E4" s="2" t="n">
-        <v>12.29</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>2.79</v>
-      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分74.0分（基本面94.0/技术面54.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -705,12 +693,8 @@
           <t>48.46</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>36.21</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.81</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分72.0分（基本面84.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -763,12 +747,8 @@
           <t>89.18</t>
         </is>
       </c>
-      <c r="E6" s="2" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>3.06</v>
-      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
           <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -821,12 +801,8 @@
           <t>1392.05</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>21.18</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>6.42</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分69.5分（基本面73.0/技术面66.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -879,12 +855,8 @@
           <t>45.60</t>
         </is>
       </c>
-      <c r="E8" s="2" t="n">
-        <v>19.47</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>2.96</v>
-      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
           <t>综合评分64.5分（基本面84.0/技术面45.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
